--- a/p6_deployment/data/france/data_preparation/df_selected_nan.xlsx
+++ b/p6_deployment/data/france/data_preparation/df_selected_nan.xlsx
@@ -557,50 +557,50 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.777835937362587</v>
+        <v>-0.7536027744523659</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3782346486220196</v>
+        <v>0.5853999441113004</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.714015051677351</v>
+        <v>-1.710726322856339</v>
       </c>
       <c r="P2" t="n">
-        <v>1.220001986947796</v>
+        <v>1.399383412370025</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-2.193886937004666</v>
+        <v>-2.187872659869627</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9283699676554468</v>
+        <v>-0.9148855700523763</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>ripawyyS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.7733859245982853</v>
+        <v>-0.3894305901184459</v>
       </c>
       <c r="C3" t="n">
-        <v>1.16664331141238</v>
+        <v>0.3728460093059502</v>
       </c>
       <c r="D3" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.4827595448698438</v>
+        <v>0.5994114795038209</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02206240018293621</v>
+        <v>-0.4230336965309512</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -618,50 +618,50 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05812538110440921</v>
+        <v>-0.7197588861487175</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1.455925603534503</v>
+        <v>1.073726552573447</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3470702783156263</v>
+        <v>-1.486016543356919</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3469380674597103</v>
+        <v>0.2765301572820125</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2966936822993745</v>
+        <v>-1.928324284698924</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2900712621315267</v>
+        <v>-0.6202917103051337</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>SOLVXEbk</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4975062325299829</v>
+        <v>-0.9576844851486082</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.426790339990133</v>
+        <v>-0.937463235951923</v>
       </c>
       <c r="D4" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.9637244445914727</v>
+        <v>-1.08396566952188</v>
       </c>
       <c r="F4" t="n">
-        <v>0.912254593610711</v>
+        <v>-0.4230336965309512</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -679,50 +679,50 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2307930041882987</v>
+        <v>-4.321737840664614</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.334513553448035</v>
+        <v>0.5387642236090109</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2037343668873698</v>
+        <v>-2.21691608081523</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7243698138288894</v>
+        <v>-0.6840045528890704</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.3010265416761491</v>
+        <v>-2.418844487076638</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4174474029886757</v>
+        <v>-2.909746183648325</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>0js8u60b</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.3932701434632443</v>
+        <v>-0.8924120782870355</v>
       </c>
       <c r="C5" t="n">
-        <v>1.617911640692062</v>
+        <v>0.008569165188616109</v>
       </c>
       <c r="D5" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1220358700786222</v>
+        <v>-0.6030007698002511</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02206240018293621</v>
+        <v>0.4671584968968236</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -740,50 +740,50 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1584769715044253</v>
+        <v>-0.6639009246746093</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.724638800986005</v>
+        <v>-0.1186884715524711</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1495061780191791</v>
+        <v>-0.4937818548535572</v>
       </c>
       <c r="P5" t="n">
-        <v>0.06084881322928617</v>
+        <v>-1.424789259563918</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.09246720677651696</v>
+        <v>-1.207701268924864</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3607393802521971</v>
+        <v>-0.1417581338347341</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>fHYrsJy3</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.468913228763976</v>
+        <v>-1.522098826833972</v>
       </c>
       <c r="C6" t="n">
-        <v>1.324315378269136</v>
+        <v>0.329350266724776</v>
       </c>
       <c r="D6" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1184465797821922</v>
+        <v>0.3589290296430066</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4671584968968236</v>
+        <v>0.912254593610711</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -801,50 +801,50 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.2742901703510408</v>
+        <v>1.042747154420003</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8140201269623039</v>
+        <v>-0.5728859845986826</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4643065567246272</v>
+        <v>1.394780649357683</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7737031956749881</v>
+        <v>0.2468495194561639</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.7749333974389941</v>
+        <v>1.155621442739104</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2857978486526689</v>
+        <v>0.4710238938772716</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>M5VGwpVA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.3894305901184459</v>
+        <v>-0.7733859245982853</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3728460093059502</v>
+        <v>1.16664331141238</v>
       </c>
       <c r="D7" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5994114795038209</v>
+        <v>-0.4827595448698438</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4230336965309512</v>
+        <v>0.02206240018293621</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -862,50 +862,50 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7458621781191507</v>
+        <v>0.03938187553374622</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.07622858432701</v>
+        <v>1.484198622221282</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.512314807688341</v>
+        <v>0.3138556709367313</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1326897438749545</v>
+        <v>-0.3769738259911923</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>-1.929308987426607</v>
+        <v>0.2225774674068451</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6997640280283157</v>
+        <v>-0.2708629064086946</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>jqSiuc6F</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1.522098826833972</v>
+        <v>1.468913228763976</v>
       </c>
       <c r="C8" t="n">
-        <v>0.329350266724776</v>
+        <v>1.324315378269136</v>
       </c>
       <c r="D8" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3589290296430066</v>
+        <v>0.1184465797821922</v>
       </c>
       <c r="F8" t="n">
-        <v>0.912254593610711</v>
+        <v>0.4671584968968236</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -923,50 +923,50 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1.135895947657537</v>
+        <v>-0.2517284375990239</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5503910140556628</v>
+        <v>0.7936529458670967</v>
       </c>
       <c r="O8" t="n">
-        <v>1.405702073277285</v>
+        <v>-0.4669472653697273</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4284061124797505</v>
+        <v>0.6958862230090092</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.233157212545089</v>
+        <v>-0.7471086841674456</v>
       </c>
       <c r="S8" t="n">
-        <v>0.603630036746598</v>
+        <v>-0.3297433060549251</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>6ehlLyFq</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.9576844851486082</v>
+        <v>-0.3932701434632443</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.937463235951923</v>
+        <v>1.617911640692062</v>
       </c>
       <c r="D9" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.08396566952188</v>
+        <v>-0.1220358700786222</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4230336965309512</v>
+        <v>0.02206240018293621</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -984,50 +984,50 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>-4.296570954603666</v>
+        <v>0.1736881474204321</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6375932205722816</v>
+        <v>-1.687248304348533</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.164610013935494</v>
+        <v>-0.1335477561991667</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7592905044157524</v>
+        <v>0.0615483426751338</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>-2.390269482651901</v>
+        <v>0.2178899490678367</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.936290326281671</v>
+        <v>-0.3328776228653583</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>zkPwWhT1</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.8924120782870355</v>
+        <v>0.4975062325299829</v>
       </c>
       <c r="C10" t="n">
-        <v>0.008569165188616109</v>
+        <v>-1.426790339990133</v>
       </c>
       <c r="D10" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6030007698002511</v>
+        <v>-0.9637244445914727</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4671584968968236</v>
+        <v>0.912254593610711</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1045,28 +1045,28 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6980539903787546</v>
+        <v>0.2141805952783453</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1812548559411186</v>
+        <v>-1.299421897714226</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4977245237737955</v>
+        <v>-0.1970013220881307</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.412024279555312</v>
+        <v>0.5987465846943708</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>-1.185613813466916</v>
+        <v>-0.2958557157926807</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2202726412405562</v>
+        <v>-0.2938575195335348</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/france/data_preparation/df_selected_nan.xlsx
+++ b/p6_deployment/data/france/data_preparation/df_selected_nan.xlsx
@@ -679,28 +679,28 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-4.321737840664614</v>
+        <v>-4.47451797258758</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5387642236090109</v>
+        <v>0.5228651459526644</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.21691608081523</v>
+        <v>-2.211550777216878</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6840045528890704</v>
+        <v>-0.705896575626916</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-2.418844487076638</v>
+        <v>-2.471400014010787</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.909746183648325</v>
+        <v>-2.954548901695158</v>
       </c>
     </row>
     <row r="5">
@@ -868,10 +868,10 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.484198622221282</v>
+        <v>1.49404553512924</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3138556709367313</v>
+        <v>0.32287410199643</v>
       </c>
       <c r="P7" t="n">
         <v>-0.3769738259911923</v>

--- a/p6_deployment/data/france/data_preparation/df_selected_nan.xlsx
+++ b/p6_deployment/data/france/data_preparation/df_selected_nan.xlsx
@@ -557,50 +557,50 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.7536027744523659</v>
+        <v>-0.7879773515073688</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5853999441113004</v>
+        <v>0.003698636191251414</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.710726322856339</v>
+        <v>-1.819703804861894</v>
       </c>
       <c r="P2" t="n">
-        <v>1.399383412370025</v>
+        <v>1.52381337741282</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-2.187872659869627</v>
+        <v>-2.141032525081042</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9148855700523763</v>
+        <v>-0.9280512712835256</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>M5VGwpVA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.3894305901184459</v>
+        <v>-0.7733859245982853</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3728460093059502</v>
+        <v>1.16664331141238</v>
       </c>
       <c r="D3" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5994114795038209</v>
+        <v>-0.4827595448698438</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4230336965309512</v>
+        <v>0.02206240018293621</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -618,50 +618,50 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.7197588861487175</v>
+        <v>0.01747659284595973</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1.073726552573447</v>
+        <v>1.203876309128134</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.486016543356919</v>
+        <v>0.3182801206980313</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2765301572820125</v>
+        <v>-0.3727279152224804</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>-1.928324284698924</v>
+        <v>0.1398101616904921</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6202917103051337</v>
+        <v>-0.2233300200720767</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>zkPwWhT1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.9576844851486082</v>
+        <v>0.4975062325299829</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.937463235951923</v>
+        <v>-1.426790339990133</v>
       </c>
       <c r="D4" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.08396566952188</v>
+        <v>-0.9637244445914727</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4230336965309512</v>
+        <v>0.912254593610711</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -679,50 +679,50 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-4.47451797258758</v>
+        <v>0.3506936338275363</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5228651459526644</v>
+        <v>-1.510720973424865</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.211550777216878</v>
+        <v>-0.2063250582212901</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.705896575626916</v>
+        <v>0.8524774529504762</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-2.471400014010787</v>
+        <v>-0.07950524125449066</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.954548901695158</v>
+        <v>-0.3435610360987559</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>6ehlLyFq</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.8924120782870355</v>
+        <v>-0.3932701434632443</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008569165188616109</v>
+        <v>1.617911640692062</v>
       </c>
       <c r="D5" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6030007698002511</v>
+        <v>-0.1220358700786222</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4671584968968236</v>
+        <v>0.02206240018293621</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -740,50 +740,50 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6639009246746093</v>
+        <v>0.1562604235505738</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1186884715524711</v>
+        <v>-1.69190583136871</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4937818548535572</v>
+        <v>-0.01744960318108858</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.424789259563918</v>
+        <v>0.2558118088057086</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>-1.207701268924864</v>
+        <v>0.1547627093041108</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1417581338347341</v>
+        <v>-0.3755432431186783</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>jqSiuc6F</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1.522098826833972</v>
+        <v>1.468913228763976</v>
       </c>
       <c r="C6" t="n">
-        <v>0.329350266724776</v>
+        <v>1.324315378269136</v>
       </c>
       <c r="D6" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3589290296430066</v>
+        <v>0.1184465797821922</v>
       </c>
       <c r="F6" t="n">
-        <v>0.912254593610711</v>
+        <v>0.4671584968968236</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -801,50 +801,50 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1.042747154420003</v>
+        <v>-0.4463210421262403</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5728859845986826</v>
+        <v>0.5711089222829272</v>
       </c>
       <c r="O6" t="n">
-        <v>1.394780649357683</v>
+        <v>-0.5010332776414956</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2468495194561639</v>
+        <v>0.9744616073713748</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.155621442739104</v>
+        <v>-1.025806407101098</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4710238938772716</v>
+        <v>-0.3259533119565321</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>ripawyyS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.7733859245982853</v>
+        <v>-0.3894305901184459</v>
       </c>
       <c r="C7" t="n">
-        <v>1.16664331141238</v>
+        <v>0.3728460093059502</v>
       </c>
       <c r="D7" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4827595448698438</v>
+        <v>0.5994114795038209</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02206240018293621</v>
+        <v>-0.4230336965309512</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -862,50 +862,50 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03938187553374622</v>
+        <v>-0.8648036532239175</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.49404553512924</v>
+        <v>1.120870003711796</v>
       </c>
       <c r="O7" t="n">
-        <v>0.32287410199643</v>
+        <v>-1.445824403807327</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3769738259911923</v>
+        <v>-0.2343696826820265</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2225774674068451</v>
+        <v>-1.993763548507826</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2708629064086946</v>
+        <v>-0.8087022755812063</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>fHYrsJy3</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.468913228763976</v>
+        <v>-1.522098826833972</v>
       </c>
       <c r="C8" t="n">
-        <v>1.324315378269136</v>
+        <v>0.329350266724776</v>
       </c>
       <c r="D8" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1184465797821922</v>
+        <v>0.3589290296430066</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4671584968968236</v>
+        <v>0.912254593610711</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -923,50 +923,50 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2517284375990239</v>
+        <v>1.338978145815176</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7936529458670967</v>
+        <v>-0.5722389018497528</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4669472653697273</v>
+        <v>1.412828469262016</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6958862230090092</v>
+        <v>0.3482982959670741</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.7471086841674456</v>
+        <v>1.372937248667634</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3297433060549251</v>
+        <v>0.820525674177228</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>SOLVXEbk</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.3932701434632443</v>
+        <v>-0.9576844851486082</v>
       </c>
       <c r="C9" t="n">
-        <v>1.617911640692062</v>
+        <v>-0.937463235951923</v>
       </c>
       <c r="D9" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1220358700786222</v>
+        <v>-1.08396566952188</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02206240018293621</v>
+        <v>-0.4230336965309512</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -984,50 +984,50 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1736881474204321</v>
+        <v>-4.675514704813494</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.687248304348533</v>
+        <v>0.4571694629792017</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1335477561991667</v>
+        <v>-1.926591745231298</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0615483426751338</v>
+        <v>-0.663995461390644</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2178899490678367</v>
+        <v>-2.165405228850827</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3328776228653583</v>
+        <v>-3.020482976480897</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>0js8u60b</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4975062325299829</v>
+        <v>-0.8924120782870355</v>
       </c>
       <c r="C10" t="n">
-        <v>-1.426790339990133</v>
+        <v>0.008569165188616109</v>
       </c>
       <c r="D10" t="n">
         <v>-0.3314773970536329</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9637244445914727</v>
+        <v>-0.6030007698002511</v>
       </c>
       <c r="F10" t="n">
-        <v>0.912254593610711</v>
+        <v>0.4671584968968236</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1045,28 +1045,28 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2141805952783453</v>
+        <v>-0.7402572120286448</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.299421897714226</v>
+        <v>-0.2686079151586224</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1970013220881307</v>
+        <v>-0.5042702675409887</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5987465846943708</v>
+        <v>-1.355221391018643</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.2958557157926807</v>
+        <v>-1.016486953456587</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2938575195335348</v>
+        <v>-0.3249279581803695</v>
       </c>
     </row>
   </sheetData>
